--- a/employee_surveys/043_leadership_ai_feedback_survey--employee_surveys.xlsx
+++ b/employee_surveys/043_leadership_ai_feedback_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'sales',_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Sales', 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'marketing',_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Marketing', 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'it',_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'IT', 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'hr',_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'HR', 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'always',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Always', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'often',_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Often', 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'sometimes',_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Sometimes', 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'important',_'label':_'important'}</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Important', 'label': 'Important'}</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_at_all',_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not at all', 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
